--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.57011</v>
+        <v>17.10382</v>
       </c>
       <c r="D2" t="n">
-        <v>16.51785</v>
+        <v>16.38703</v>
       </c>
       <c r="E2" t="n">
-        <v>16.41902</v>
+        <v>16.68339</v>
       </c>
       <c r="F2" t="n">
-        <v>42.8283</v>
+        <v>42.79722</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05027</v>
+        <v>0.0508</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81888</v>
+        <v>1.85665</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.83272</v>
+        <v>17.03624</v>
       </c>
       <c r="D3" t="n">
-        <v>16.55035</v>
+        <v>16.11804</v>
       </c>
       <c r="E3" t="n">
-        <v>16.88037</v>
+        <v>16.75651</v>
       </c>
       <c r="F3" t="n">
-        <v>43.00385</v>
+        <v>42.32448</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0503</v>
+        <v>0.04942</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81854</v>
+        <v>1.85502</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.24661</v>
+        <v>16.88704</v>
       </c>
       <c r="D4" t="n">
-        <v>16.38302</v>
+        <v>16.66531</v>
       </c>
       <c r="E4" t="n">
-        <v>17.0115</v>
+        <v>16.73196</v>
       </c>
       <c r="F4" t="n">
-        <v>42.52992</v>
+        <v>41.58705</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04984</v>
+        <v>0.05041</v>
       </c>
       <c r="H4" t="n">
-        <v>1.78948</v>
+        <v>1.79959</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.63994</v>
+        <v>16.64926</v>
       </c>
       <c r="D6" t="n">
-        <v>15.75498</v>
+        <v>15.81343</v>
       </c>
       <c r="E6" t="n">
-        <v>16.53723</v>
+        <v>16.59245</v>
       </c>
       <c r="F6" t="n">
-        <v>21.71191</v>
+        <v>21.69443</v>
       </c>
       <c r="G6" t="n">
-        <v>34.05008</v>
+        <v>34.811</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.34449</v>
+        <v>16.58221</v>
       </c>
       <c r="D7" t="n">
-        <v>15.72685</v>
+        <v>15.67439</v>
       </c>
       <c r="E7" t="n">
-        <v>16.2138</v>
+        <v>16.26932</v>
       </c>
       <c r="F7" t="n">
-        <v>22.04522</v>
+        <v>21.39423</v>
       </c>
       <c r="G7" t="n">
-        <v>33.46118</v>
+        <v>34.61377</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.52016</v>
+        <v>16.70334</v>
       </c>
       <c r="D8" t="n">
-        <v>15.9034</v>
+        <v>16.11355</v>
       </c>
       <c r="E8" t="n">
-        <v>16.34507</v>
+        <v>16.53443</v>
       </c>
       <c r="F8" t="n">
-        <v>21.50608</v>
+        <v>21.57432</v>
       </c>
       <c r="G8" t="n">
-        <v>33.23049</v>
+        <v>34.15425</v>
       </c>
     </row>
   </sheetData>
